--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485478</t>
         </is>
       </c>
     </row>
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79548443</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75153005</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75190670</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129843045</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102829427</t>
         </is>
       </c>
     </row>
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100973803</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1602,6 +1642,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101053048</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,6 +1766,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75149372</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1840,6 +1890,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75149520</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1946,6 +2001,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485479</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2052,6 +2112,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485480</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2178,6 +2243,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132142419</t>
         </is>
       </c>
     </row>
@@ -2287,6 +2357,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75147532</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2394,8 +2469,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75152209</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1650,64 +1650,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75149372</v>
+        <v>135671771</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>56859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>205995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558022</v>
+        <v>558039</v>
       </c>
       <c r="R10" t="n">
-        <v>6632396</v>
+        <v>6632490</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1731,12 +1728,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Registrering med autobox (384 kHz) under natten 4–5 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Dvärgpipistrell registrerades vid flera tillfällen med hög klassificeringssäkerhet. Fynden visar att arten förekommer på lokalen och sannolikt utnyttjar området för födosök.                                               Ljudboxen var placerad i sumpskogsområde, med äldre träd och i anslutning till en glänta. Området utgör en varierad skogsmiljö och således sannolikt med god tillgång på nattflygande insekter.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,93 +1757,80 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre mossig barrblandskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75149372</t>
+          <t>https://artportalen.se/Sighting/135671771</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>75149520</v>
+        <v>135671557</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>56838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>205998</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558023</v>
+        <v>558039</v>
       </c>
       <c r="R11" t="n">
-        <v>6632379</v>
+        <v>6632490</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1855,12 +1854,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Registrering med autobox (384 kHz) under natten 4–5 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid upprepade tillfällen med hög klassificeringssäkerhet. Registreringarna tyder på att området används som födosöksområde.                                                                 Ljudboxen var placerad i sumpskogsområde, med äldre träd och i anslutning till en glänta. Området utgör en varierad skogsmiljö och således sannolikt med god tillgång på nattflygande insekter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,36 +1883,35 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre mossig barrblandskog</t>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75149520</t>
+          <t>https://artportalen.se/Sighting/135671557</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485479</v>
+        <v>75149372</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1926,20 +1939,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557848</v>
+        <v>558022</v>
       </c>
       <c r="R12" t="n">
         <v>6632396</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,12 +1992,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,39 +2006,36 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Äldre granblandad tallskog</t>
+          <t>Äldre mossig barrblandskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122485479</t>
+          <t>https://artportalen.se/Sighting/75149372</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485480</v>
+        <v>75149520</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -2037,20 +2063,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558014</v>
+        <v>558023</v>
       </c>
       <c r="R13" t="n">
-        <v>6632392</v>
+        <v>6632379</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2074,12 +2116,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,42 +2130,39 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre barrskog, nordsluttning</t>
+          <t>Äldre mossig barrblandskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122485480</t>
+          <t>https://artportalen.se/Sighting/75149520</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132142419</v>
+        <v>122485479</v>
       </c>
       <c r="B14" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2148,36 +2187,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs sn, Vstm</t>
+          <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557834</v>
+        <v>557848</v>
       </c>
       <c r="R14" t="n">
-        <v>6632371</v>
+        <v>6632396</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,22 +2224,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,80 +2238,80 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Thomas Janzon</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Skogsprojektet</t>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132142419</t>
+          <t>https://artportalen.se/Sighting/122485479</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>75147532</v>
+        <v>122485480</v>
       </c>
       <c r="B15" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558215</v>
+        <v>558014</v>
       </c>
       <c r="R15" t="n">
-        <v>6632574</v>
+        <v>6632392</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2322,12 +2335,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,81 +2349,96 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallmosse</t>
+          <t>Äldre barrskog, nordsluttning</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75147532</t>
+          <t>https://artportalen.se/Sighting/122485480</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>75152209</v>
+        <v>132142419</v>
       </c>
       <c r="B16" t="n">
-        <v>97983</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557831</v>
+        <v>557834</v>
       </c>
       <c r="R16" t="n">
-        <v>6632505</v>
+        <v>6632371</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2434,12 +2462,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,24 +2490,247 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Mosse med tall, björk, gran</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Thomas Janzon</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132142419</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>75147532</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558215</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6632574</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75147532</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>75152209</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>557831</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6632505</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Mosse med tall, björk, gran</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/75152209</t>
         </is>
@@ -2492,6 +2753,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,51 +912,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>75153005</v>
+        <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>91872</v>
+        <v>93345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bockmossen S, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558180</v>
+        <v>558387</v>
       </c>
       <c r="R4" t="n">
-        <v>6632659</v>
+        <v>6632344</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,12 +988,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Från förra året</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,37 +1021,32 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog, inslag av björk</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Gran, undersidan på klen låga, nedsänkt i mossa</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75153005</t>
+          <t>https://artportalen.se/Sighting/135727895</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75190670</v>
+        <v>75153005</v>
       </c>
       <c r="B5" t="n">
         <v>91872</v>
@@ -1062,17 +1080,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Bockmossen S, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557842</v>
+        <v>558180</v>
       </c>
       <c r="R5" t="n">
-        <v>6632447</v>
+        <v>6632659</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,12 +1114,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-12-05</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-12-05</t>
+          <t>2018-12-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1139,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Gran, undersidan på klen låga, nedsänkt i mossa</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,16 +1156,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75190670</t>
+          <t>https://artportalen.se/Sighting/75153005</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129843045</v>
+        <v>75190670</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,53 +1173,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558530</v>
+        <v>557842</v>
       </c>
       <c r="R6" t="n">
-        <v>6632482</v>
+        <v>6632447</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,17 +1230,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2018-12-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Kan inte avgöra om det var en tupp eller en höna som hade skitit på platsen!</t>
+          <t>2018-12-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,33 +1244,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog, inslag av björk</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129843045</t>
+          <t>https://artportalen.se/Sighting/75190670</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102829427</v>
+        <v>129843045</v>
       </c>
       <c r="B7" t="n">
-        <v>58439</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,21 +1289,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1300,19 +1311,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1322,17 +1325,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Målsjövägen, Ramnäs, Vstm, Vstm</t>
+          <t>Sylbergen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558653</v>
+        <v>558530</v>
       </c>
       <c r="R7" t="n">
-        <v>6632198</v>
+        <v>6632482</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,22 +1359,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kan inte avgöra om det var en tupp eller en höna som hade skitit på platsen!</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,40 +1380,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102829427</t>
+          <t>https://artportalen.se/Sighting/129843045</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100973803</v>
+        <v>102829427</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>58439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,46 +1412,61 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>103018</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bockmossen, Ramnäs sn, Vstm</t>
+          <t>Målsjövägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558147</v>
+        <v>558653</v>
       </c>
       <c r="R8" t="n">
-        <v>6632664</v>
+        <v>6632198</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,17 +1490,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På talllåga</t>
+          <t>2022-08-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,34 +1514,42 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100973803</t>
+          <t>https://artportalen.se/Sighting/102829427</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101053048</v>
+        <v>135762366</v>
       </c>
       <c r="B9" t="n">
-        <v>8455</v>
+        <v>58255</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,50 +1557,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>103019</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs, Vstm , Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558083</v>
+        <v>558383</v>
       </c>
       <c r="R9" t="n">
-        <v>6632631</v>
+        <v>6632336</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,12 +1620,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,7 +1644,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1638,76 +1660,69 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101053048</t>
+          <t>https://artportalen.se/Sighting/135762366</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>75149372</v>
+        <v>135762156</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>58141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558022</v>
+        <v>558379</v>
       </c>
       <c r="R10" t="n">
-        <v>6632396</v>
+        <v>6632329</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1731,12 +1746,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,61 +1770,60 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre mossig barrblandskog</t>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75149372</t>
+          <t>https://artportalen.se/Sighting/135762156</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>75149520</v>
+        <v>135762179</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1807,31 +1831,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm, Sylbergen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558023</v>
+        <v>558384</v>
       </c>
       <c r="R11" t="n">
-        <v>6632379</v>
+        <v>6632336</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1855,12 +1872,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,77 +1896,85 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre mossig barrblandskog</t>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75149520</t>
+          <t>https://artportalen.se/Sighting/135762179</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122485479</v>
+        <v>100973803</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Bockmossen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557848</v>
+        <v>558147</v>
       </c>
       <c r="R12" t="n">
-        <v>6632396</v>
+        <v>6632664</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1963,12 +1998,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2022-05-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På talllåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,80 +2017,85 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre granblandad tallskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122485479</t>
+          <t>https://artportalen.se/Sighting/100973803</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122485480</v>
+        <v>101053048</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558014</v>
+        <v>558083</v>
       </c>
       <c r="R13" t="n">
-        <v>6632392</v>
+        <v>6632631</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2074,12 +2119,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2022-05-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,96 +2133,90 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre barrskog, nordsluttning</t>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tommy Pettersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Pia Hagfors, Bengt Eriksson, Seppo Ormiskangas, Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122485480</t>
+          <t>https://artportalen.se/Sighting/101053048</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132142419</v>
+        <v>135671771</v>
       </c>
       <c r="B14" t="n">
-        <v>99195</v>
+        <v>56859</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sylbergen, Ramnäs sn, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557834</v>
+        <v>558039</v>
       </c>
       <c r="R14" t="n">
-        <v>6632371</v>
+        <v>6632490</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2201,22 +2240,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Registrering med autobox (384 kHz) under natten 4–5 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Dvärgpipistrell registrerades vid flera tillfällen med hög klassificeringssäkerhet. Fynden visar att arten förekommer på lokalen och sannolikt utnyttjar området för födosök.                                               Ljudboxen var placerad i sumpskogsområde, med äldre träd och i anslutning till en glänta. Området utgör en varierad skogsmiljö och således sannolikt med god tillgång på nattflygande insekter.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,38 +2269,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Thomas Janzon</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132142419</t>
+          <t>https://artportalen.se/Sighting/135671771</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>75147532</v>
+        <v>135779481</v>
       </c>
       <c r="B15" t="n">
-        <v>97983</v>
+        <v>56859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,41 +2303,50 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>205995</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558215</v>
+        <v>558382</v>
       </c>
       <c r="R15" t="n">
-        <v>6632574</v>
+        <v>6632335</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2322,12 +2370,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz) i skogsmiljö i Sylbergen. Inspelningarna analyserades med BTO Acoustic Pipeline. Dvärgpipistrell registrerades vid flera tillfällen. De starkaste registreringarna gjordes den 8 augusti kl. 00:19 med hög klassificeringssäkerhet och den 7 augusti kl. 21:56.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,78 +2399,82 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Tallmosse</t>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75147532</t>
+          <t>https://artportalen.se/Sighting/135779481</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>75152209</v>
+        <v>135671557</v>
       </c>
       <c r="B16" t="n">
-        <v>97983</v>
+        <v>56838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sylbergen, Vstm</t>
+          <t>Sylbergen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>557831</v>
+        <v>558039</v>
       </c>
       <c r="R16" t="n">
-        <v>6632505</v>
+        <v>6632490</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2434,12 +2501,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-12-04</t>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>00:35</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Registrering med autobox (384 kHz) under natten 4–5 augusti 2026. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid upprepade tillfällen med hög klassificeringssäkerhet. Registreringarna tyder på att området används som födosöksområde.                                                                 Ljudboxen var placerad i sumpskogsområde, med äldre träd och i anslutning till en glänta. Området utgör en varierad skogsmiljö och således sannolikt med god tillgång på nattflygande insekter.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2448,28 +2530,1120 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Mosse med tall, björk, gran</t>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Tallsumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135671557</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135779311</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56838</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sylbergen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558382</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6632335</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz) i skogsmiljö i Sylbergen. Inspelningarna analyserades med BTO Acoustic Pipeline. Nordfladdermus registrerades vid flera tillfällen. Den starkaste registreringen gjordes den 8 augusti kl. 01:55 med hög klassificeringssäkerhet och arten registrerades även efterföljande natt.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135779311</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135779178</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56861</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>aktiv</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sylbergen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>558382</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6632335</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Registrerad med autobox (384 kHz) i skogsmiljö i Sylbergen. Inspelningen analyserades med BTO Acoustic Pipeline. Brunlångöra registrerades vid två skilda tillfällen den 8:e augusti med hög klassificeringssäkerhet.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135779178</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>75149372</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>558022</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6632396</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre mossig barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75149372</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>75149520</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>558023</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6632379</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre mossig barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75149520</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122485479</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>557848</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6632396</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre granblandad tallskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485479</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122485480</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>558014</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6632392</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Äldre barrskog, nordsluttning</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Aivars Dunskis</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122485480</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132142419</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sylbergen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>557834</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6632371</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Thomas Janzon</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132142419</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>75147532</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>558215</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6632574</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Tallmosse</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75147532</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>75152209</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sylbergen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>557831</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6632505</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2018-12-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Mosse med tall, björk, gran</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/75152209</t>
         </is>
@@ -2492,6 +3666,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>135762366</v>
       </c>
       <c r="B9" t="n">
-        <v>58255</v>
+        <v>58257</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135762156</v>
       </c>
       <c r="B10" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135762179</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135671771</v>
       </c>
       <c r="B14" t="n">
-        <v>56859</v>
+        <v>56861</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>135779481</v>
       </c>
       <c r="B15" t="n">
-        <v>56859</v>
+        <v>56861</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>135671557</v>
       </c>
       <c r="B16" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>135779311</v>
       </c>
       <c r="B17" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>135779178</v>
       </c>
       <c r="B18" t="n">
-        <v>56861</v>
+        <v>56863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>135762366</v>
       </c>
       <c r="B9" t="n">
-        <v>58257</v>
+        <v>58258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135762156</v>
       </c>
       <c r="B10" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135762179</v>
       </c>
       <c r="B11" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135671771</v>
       </c>
       <c r="B14" t="n">
-        <v>56861</v>
+        <v>56862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>135779481</v>
       </c>
       <c r="B15" t="n">
-        <v>56861</v>
+        <v>56862</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>135671557</v>
       </c>
       <c r="B16" t="n">
-        <v>56840</v>
+        <v>56841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>135779311</v>
       </c>
       <c r="B17" t="n">
-        <v>56840</v>
+        <v>56841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>135779178</v>
       </c>
       <c r="B18" t="n">
-        <v>56863</v>
+        <v>56864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>135762366</v>
       </c>
       <c r="B9" t="n">
-        <v>58258</v>
+        <v>58262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135762156</v>
       </c>
       <c r="B10" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135762179</v>
       </c>
       <c r="B11" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135671771</v>
       </c>
       <c r="B14" t="n">
-        <v>56862</v>
+        <v>56866</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>135779481</v>
       </c>
       <c r="B15" t="n">
-        <v>56862</v>
+        <v>56866</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>135671557</v>
       </c>
       <c r="B16" t="n">
-        <v>56841</v>
+        <v>56845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>135779311</v>
       </c>
       <c r="B17" t="n">
-        <v>56841</v>
+        <v>56845</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>135779178</v>
       </c>
       <c r="B18" t="n">
-        <v>56864</v>
+        <v>56868</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>135762366</v>
       </c>
       <c r="B9" t="n">
-        <v>58262</v>
+        <v>58263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135762156</v>
       </c>
       <c r="B10" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135762179</v>
       </c>
       <c r="B11" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>135671771</v>
       </c>
       <c r="B14" t="n">
-        <v>56866</v>
+        <v>56867</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>135779481</v>
       </c>
       <c r="B15" t="n">
-        <v>56866</v>
+        <v>56867</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>135671557</v>
       </c>
       <c r="B16" t="n">
-        <v>56845</v>
+        <v>56846</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>135779311</v>
       </c>
       <c r="B17" t="n">
-        <v>56845</v>
+        <v>56846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>135779178</v>
       </c>
       <c r="B18" t="n">
-        <v>56868</v>
+        <v>56869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -915,7 +915,7 @@
         <v>135727895</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>135762366</v>
       </c>
       <c r="B9" t="n">
-        <v>58263</v>
+        <v>58268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135762156</v>
       </c>
       <c r="B10" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135762179</v>
       </c>
       <c r="B11" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>135779481</v>
       </c>
       <c r="B15" t="n">
-        <v>56867</v>
+        <v>56872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>135779311</v>
       </c>
       <c r="B17" t="n">
-        <v>56846</v>
+        <v>56851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>135779178</v>
       </c>
       <c r="B18" t="n">
-        <v>56869</v>
+        <v>56874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/S 2049-2026 artfynd.xlsx
+++ b/artfynd/S 2049-2026 artfynd.xlsx
@@ -1549,7 +1549,7 @@
         <v>135762366</v>
       </c>
       <c r="B9" t="n">
-        <v>58268</v>
+        <v>58281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>135762156</v>
       </c>
       <c r="B10" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>135762179</v>
       </c>
       <c r="B11" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
